--- a/docs/thong_ke_mo_ta.xlsx
+++ b/docs/thong_ke_mo_ta.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -513,6 +513,11 @@
           <t>std[S] theo gio (phut)</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Ket luan Poisson (alpha=0.05)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -558,6 +563,11 @@
       <c r="M2" t="n">
         <v>2.83</v>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Bác bỏ (nhẹ)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -603,6 +613,11 @@
       <c r="M3" t="n">
         <v>3.74</v>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Bác bỏ (nhẹ)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -648,6 +663,11 @@
       <c r="M4" t="n">
         <v>3.08</v>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Bác bỏ (mạnh)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -693,6 +713,11 @@
       <c r="M5" t="n">
         <v>2.95</v>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Bác bỏ (mạnh)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -738,6 +763,11 @@
       <c r="M6" t="n">
         <v>3</v>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Chưa bác bỏ</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -783,6 +813,11 @@
       <c r="M7" t="n">
         <v>3.07</v>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Bác bỏ (mạnh)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -828,6 +863,11 @@
       <c r="M8" t="n">
         <v>3.34</v>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Bác bỏ (mạnh)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -873,6 +913,11 @@
       <c r="M9" t="n">
         <v>3.24</v>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Bác bỏ (mạnh)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -917,6 +962,11 @@
       </c>
       <c r="M10" t="n">
         <v>2.82</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Bác bỏ (nhẹ)</t>
+        </is>
       </c>
     </row>
   </sheetData>
